--- a/naver-place-crawler/results_nail/영도구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/영도구_네일샵.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일하버</t>
+          <t>손이예쁜그녀</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ha01066@naver.com</t>
+          <t>nail_won@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1476-9929</t>
+          <t>051-404-4141</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중구로24번길 21-2 2층</t>
+          <t>부산광역시 영도구 동삼로 89 손이예쁜그녀</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_habor.studio?igsh=c3VpOXBsMmE3MDhk</t>
+          <t>https://www.instagram.com/nailjiwon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2072980281</t>
+          <t>36636875</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072980281</t>
+          <t>https://m.place.naver.com/place/36636875</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>쏘블링네일</t>
+          <t>남포동네일옐로</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gml94@naver.com</t>
+          <t>suhyun5618@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1367-1696</t>
+          <t>0507-1378-0493</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 중구 흑교로 83-1 3층</t>
+          <t>부산광역시 중구 남포동1가 11 41호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sso_blingnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>644</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>664</v>
+        <v>324</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1946317931</t>
+          <t>1003177563</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317931</t>
+          <t>https://m.place.naver.com/place/1003177563</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아르떼살롱</t>
+          <t>솔네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dnflaowja@naver.com</t>
+          <t>ioio93@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1329-0048</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 동구 중앙대로 181 3층</t>
+          <t>부산광역시 영도구 태종로 422 태림맨션상가 103호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/_arte_salon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +780,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1914602054</t>
+          <t>1216411669</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914602054</t>
+          <t>https://m.place.naver.com/place/1216411669</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>가이쌀롱 네일&amp;패디샵</t>
+          <t>마벨네일뷰티남포</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dbcom36@naver.com</t>
+          <t>tiia@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1342-9301</t>
+          <t>0507-1344-0730</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 13 (남포동1가21-6) 2층, 가이쌀롱</t>
+          <t>부산광역시 중구 남포길 28-1 3층 마벨네일뷰티</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://instagram.com/gai_salon_</t>
+          <t>https://www.instagram.com/_ma.belle_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1335843653</t>
+          <t>1631435764</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335843653</t>
+          <t>https://m.place.naver.com/place/1631435764</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +936,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>나나뷰티살롱</t>
+          <t>포유네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rosyn_@naver.com</t>
+          <t>nail_for_u@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1336-2115</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 557 삼창파크맨션 상가101호</t>
+          <t>부산광역시 영도구 동삼로 56 한나타워 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nana2115__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +964,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -988,22 +980,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,66 +1004,66 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1829607863</t>
+          <t>16383416</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1829607863</t>
+          <t>https://m.place.naver.com/place/16383416</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>눈썹살롱 네일살롱</t>
+          <t>뷰티3975</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sallyjuli@naver.com</t>
+          <t>chdbs0968@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1375-4952</t>
+          <t>0507-1373-0968</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로49번길 52 1층</t>
+          <t>부산광역시 중구 광복로55번길 1-1 2. 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://blog.naver.com/chdbs0968</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>31</v>
+        <v>858</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="R7" t="n">
-        <v>32</v>
+        <v>1023</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1925879465</t>
+          <t>1165703720</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925879465</t>
+          <t>https://m.place.naver.com/place/1165703720</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일반하다</t>
+          <t>네일하리</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iiijuheeiii@naver.com</t>
+          <t>nobleliz_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>051-915-7022</t>
+          <t>0507-1464-4548</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로 18-1</t>
+          <t>부산광역시 영도구 동삼오션로 30 213호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://instagram.com/banhada_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>572364787</t>
+          <t>1707859953</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/572364787</t>
+          <t>https://m.place.naver.com/place/1707859953</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,24 +1214,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>손톱이야기</t>
+          <t>네일에스와이</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rexdialeon@naver.com</t>
+          <t>kcjhad109214@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>051-417-7005</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로101번길 38</t>
+          <t>부산광역시 영도구 향토길 1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1279,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1282,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36925644</t>
+          <t>1201816037</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36925644</t>
+          <t>https://m.place.naver.com/place/1201816037</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1304,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>제이민뷰티</t>
+          <t>손톱이야기</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>laputasida@naver.com</t>
+          <t>rexdialeon@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1414-3834</t>
+          <t>051-417-7005</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 중구 해관로 47-1 2층</t>
+          <t>부산광역시 영도구 절영로101번길 38</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://네일인스타https//instagram.com/j_min_nail?igshid=rr24r0p8o90u</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1336,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1369,18 +1357,18 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>46</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1388,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>269796361</t>
+          <t>36925644</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/269796361</t>
+          <t>https://m.place.naver.com/place/36925644</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1398,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>손이예쁜그녀</t>
+          <t>미소샵네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nail_won@naver.com</t>
+          <t>ehdkdlahd@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>051-404-4141</t>
+          <t>0507-1338-7038</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 89 손이예쁜그녀</t>
+          <t>부산광역시 중구 중앙대로 45 3층 301호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailjiwon</t>
+          <t>https://blog.naver.com/ehdkdlahd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1435,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>499</v>
       </c>
       <c r="R11" t="n">
-        <v>162</v>
+        <v>612</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36636875</t>
+          <t>1824109129</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36636875</t>
+          <t>https://m.place.naver.com/place/1824109129</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1504,34 +1492,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일포시즌 레푸스 남포점</t>
+          <t>오몽네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mimongmnn@naver.com</t>
+          <t>olmang_nail@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1498-2303</t>
+          <t>0507-1351-4790</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 50-1 5층</t>
+          <t>부산광역시 영도구 동삼로 31 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://litt.ly/refuss_nail4season_busan</t>
+          <t>https://blog.naver.com/olmang_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1541,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>873</v>
+        <v>522</v>
       </c>
       <c r="Q12" t="n">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>1012</v>
+        <v>546</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1703326180</t>
+          <t>1539347427</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703326180</t>
+          <t>https://m.place.naver.com/place/1539347427</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1598,39 +1586,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>남포동네일옐로</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>suhyun5618@naver.com</t>
-        </is>
-      </c>
+          <t>모던네일</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1378-0493</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 중구 남포동1가 11 41호</t>
+          <t>부산광역시 영도구 영선대로 81 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xcjxgPG</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1646,22 +1626,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>314</v>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1003177563</t>
+          <t>1428351678</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003177563</t>
+          <t>https://m.place.naver.com/place/1428351678</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1692,34 +1672,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>끌레르뷰티</t>
+          <t>기분전환네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>clair2022@naver.com</t>
+          <t>jisoo851208@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1301-8923</t>
+          <t>0507-1368-1158</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 중구 남포길 29-1 4층 끌레르뷰티</t>
+          <t>부산광역시 영도구 동삼북로 20 일동미라주브라이튼 1단지 상가 110호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Sxaxcvxb/chat</t>
+          <t>http://www.instagram.com/gbjh_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1740,7 +1720,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1749,13 +1729,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="Q14" t="n">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="R14" t="n">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1744,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1704404297</t>
+          <t>53146158</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704404297</t>
+          <t>https://m.place.naver.com/place/53146158</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1766,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>손꽃풀네일</t>
+          <t>미쯔네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bongjuyha@naver.com</t>
+          <t>mizz_nail@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1348-6215</t>
+          <t>0507-1388-3448</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 72 1층</t>
+          <t>부산광역시 중구 광복로 47-1 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bongjuyha</t>
+          <t>https://blog.naver.com/mizz_nail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1843,13 +1823,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q15" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="R15" t="n">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1838,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1289134648</t>
+          <t>1942024821</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1289134648</t>
+          <t>https://m.place.naver.com/place/1942024821</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1880,39 +1860,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일앤블랑</t>
+          <t>썬 네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rang-design@naver.com</t>
+          <t>sunnail3024@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1398-7040</t>
+          <t>0507-1341-0099</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로34번길 7 세컨페이스 4층</t>
+          <t>부산광역시 남구 용주로 23 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnGftxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1928,22 +1908,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="Q16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1479860666</t>
+          <t>1900035133</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479860666</t>
+          <t>https://m.place.naver.com/place/1900035133</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1974,29 +1954,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>쁨잇</t>
+          <t>쿠키네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>qpt1107@naver.com</t>
+          <t>gksrhdwn0804@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1480-4861</t>
+          <t>051-418-2939</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로 34 2층</t>
+          <t>부산광역시 영도구 대교로14번길 28</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ppeumit_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2006,7 +1986,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2027,17 +2007,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2026,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1931140160</t>
+          <t>1954239361</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931140160</t>
+          <t>https://m.place.naver.com/place/1954239361</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2068,39 +2048,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>뷰티데이</t>
+          <t>푸스케어 남포점 글림네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1208_sj@naver.com</t>
+          <t>mcnampo@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1369-7116</t>
+          <t>0507-1331-8813</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 12-1 도시철도 남포역 지하상가 21호</t>
+          <t>부산광역시 중구 구덕로 32-1 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://typebot.co/fusscarenampo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2121,17 +2101,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>121</v>
+        <v>299</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>309</v>
       </c>
       <c r="R18" t="n">
-        <v>122</v>
+        <v>608</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2120,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2080886215</t>
+          <t>1305002599</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080886215</t>
+          <t>https://m.place.naver.com/place/1305002599</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2162,25 +2142,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>달리뷰띠끄</t>
+          <t>설탕네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sonmh1122@naver.com</t>
+          <t>sos0902kr@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1400-2205</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 54-1 2층 203호</t>
+          <t>부산광역시 영도구 절영로29번길 55 설탕네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnYigT</t>
+          <t>https://toss-order.tossplace.com/booking/vfSz8GDhgdoBPnv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2190,7 +2174,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2206,7 +2190,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2215,13 +2199,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4145</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4540</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2214,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1025786243</t>
+          <t>1391812097</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025786243</t>
+          <t>https://m.place.naver.com/place/1391812097</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2236,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>르메드</t>
+          <t>오늘,네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>doitjump@naver.com</t>
+          <t>bb_syun126@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>051-417-8046</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로13번길 5 1층 RE:MADE 르메드</t>
+          <t>부산광역시 영도구 대교로 15 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_made.nail</t>
+          <t>http://www.instagram.com/2day__nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,13 +2289,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>189</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2304,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1237521512</t>
+          <t>1924350921</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237521512</t>
+          <t>https://m.place.naver.com/place/1924350921</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2346,34 +2326,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>기분전환네일</t>
+          <t>네일앤블랑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>rang-design@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1368-1158</t>
+          <t>0507-1398-7040</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼북로 20 일동미라주브라이튼 1단지 상가 110호</t>
+          <t>부산광역시 중구 구덕로34번길 7 세컨페이스 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/gbjh_nail</t>
+          <t>http://pf.kakao.com/_xnGftxj</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2394,7 +2374,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2403,13 +2383,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="Q21" t="n">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="R21" t="n">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2398,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>53146158</t>
+          <t>1479860666</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/53146158</t>
+          <t>https://m.place.naver.com/place/1479860666</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2440,25 +2420,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>모모네일</t>
+          <t>쁨잇</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>brenda70@naver.com</t>
+          <t>qpt1107@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1480-4861</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 중구 흑교로75번길 4-2 1층</t>
+          <t>부산광역시 영도구 남항로 34 2층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momonail0077</t>
+          <t>https://www.instagram.com/ppeumit_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2493,13 +2477,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2492,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1050708757</t>
+          <t>1931140160</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050708757</t>
+          <t>https://m.place.naver.com/place/1931140160</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2514,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>마벨네일뷰티남포</t>
+          <t>나나뷰티살롱</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tiia@naver.com</t>
+          <t>rosyn_@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1344-0730</t>
+          <t>0507-1336-2115</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 중구 남포길 28-1 3층 마벨네일뷰티</t>
+          <t>부산광역시 영도구 절영로 557 삼창파크맨션 상가101호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ma.belle_nail</t>
+          <t>https://www.instagram.com/nana2115__</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2587,13 +2571,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="R23" t="n">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2586,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1631435764</t>
+          <t>1829607863</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631435764</t>
+          <t>https://m.place.naver.com/place/1829607863</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2624,34 +2608,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>민네일</t>
+          <t>네일반하다</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cej909@naver.com</t>
+          <t>iiijuheeiii@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1432-9337</t>
+          <t>051-915-7022</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 531 우리마트&amp;호박터 4층</t>
+          <t>부산광역시 영도구 남항로 18-1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sGMan/friend</t>
+          <t>http://instagram.com/banhada_nail_</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2672,7 +2656,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,14 +2665,14 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>23</v>
       </c>
-      <c r="R24" t="n">
-        <v>240</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>X</t>
@@ -2696,17 +2680,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1132328251</t>
+          <t>572364787</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132328251</t>
+          <t>https://m.place.naver.com/place/572364787</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2702,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>포유네일</t>
+          <t>손톱깎끼</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nail_for_u@naver.com</t>
+          <t>dojin4538@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2731,7 +2715,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 56 한나타워 3층</t>
+          <t>부산광역시 영도구 청학로 86</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2771,13 +2755,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2770,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16383416</t>
+          <t>1961112938</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16383416</t>
+          <t>https://m.place.naver.com/place/1961112938</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2792,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>루네일공방</t>
+          <t>에스타네일 남포점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>loonails@naver.com</t>
+          <t>hoihoi1704@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1421-4101</t>
+          <t>0507-1367-1210</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복중앙로 3 루네일공방 1층 (창선파출소 옆골목)</t>
+          <t>부산광역시 중구 광복로 45-12 에스타네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/loonailsfactory</t>
+          <t>https://www.instagram.com/estarnail_</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2865,13 +2849,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="Q26" t="n">
-        <v>195</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>504</v>
+        <v>243</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2864,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>37484954</t>
+          <t>1193980987</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37484954</t>
+          <t>https://m.place.naver.com/place/1193980987</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2902,29 +2886,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>뷰티3975</t>
+          <t>네일&amp;속눈썹 마찝</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>chdbs0968@naver.com</t>
+          <t>hanna6883@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1373-0968</t>
+          <t>051-711-1101</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로55번길 1-1 2. 3층</t>
+          <t>부산광역시 영도구 웃서발로 86 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chdbs0968</t>
+          <t>https://open.kakao.com/o/sR6gMBue</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2939,7 +2923,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2950,7 +2934,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2959,13 +2943,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>854</v>
+        <v>238</v>
       </c>
       <c r="Q27" t="n">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="R27" t="n">
-        <v>1019</v>
+        <v>308</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2958,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1165703720</t>
+          <t>1958309487</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165703720</t>
+          <t>https://m.place.naver.com/place/1958309487</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2996,29 +2980,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>윤아네일</t>
+          <t>아르떼살롱</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>00miya00@naver.com</t>
+          <t>dnflaowja@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1322-6563</t>
+          <t>0507-1329-0048</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 504 상가 206호</t>
+          <t>부산광역시 동구 중앙대로 181 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_arte_salon</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3028,7 +3012,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3049,17 +3033,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3052,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1363399967</t>
+          <t>1914602054</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363399967</t>
+          <t>https://m.place.naver.com/place/1914602054</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3074,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>손톱</t>
+          <t>뷰티데이</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gertrude01@naver.com</t>
+          <t>1208_sj@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>070-8882-4003</t>
+          <t>0507-1369-7116</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 조내기로 38-1 원우엔리치빌상가 1층</t>
+          <t>부산광역시 중구 구덕로 12-1 도시철도 남포역 지하상가 21호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_young4003</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3122,7 +3106,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3143,17 +3127,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,66 +3146,66 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1299202573</t>
+          <t>2080886215</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299202573</t>
+          <t>https://m.place.naver.com/place/2080886215</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>속눈썹증모,연장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>미소샵네일</t>
+          <t>눈썹살롱 네일살롱</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ehdkdlahd@naver.com</t>
+          <t>sallyjuli@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1338-7038</t>
+          <t>0507-1375-4952</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중앙대로 45 3층 301호</t>
+          <t>부산광역시 영도구 남항로49번길 52 1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehdkdlahd</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3241,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="Q30" t="n">
-        <v>497</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>609</v>
+        <v>32</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3240,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1824109129</t>
+          <t>1925879465</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824109129</t>
+          <t>https://m.place.naver.com/place/1925879465</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3278,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>와이네일</t>
+          <t>손톱에 물들다</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9001177@naver.com</t>
+          <t>wldms141300@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1336-7730</t>
+          <t>070-8257-6168</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 140-1 2층</t>
+          <t>부산광역시 영도구 태종로292번길 23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/eunjung.c_nail</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3310,7 +3294,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3331,17 +3315,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3334,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1211642980</t>
+          <t>38262661</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1211642980</t>
+          <t>https://m.place.naver.com/place/38262661</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3372,29 +3356,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>손톱에 물들다</t>
+          <t>네일엠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>wldms141300@naver.com</t>
+          <t>kkimyuu@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>070-8257-6168</t>
+          <t>0507-1332-2366</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로292번길 23</t>
+          <t>부산광역시 중구 대청로 125 2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eunjung.c_nail</t>
+          <t>https://www.instagram.com/nail.b.m</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3429,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3428,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>38262661</t>
+          <t>1433019367</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38262661</t>
+          <t>https://m.place.naver.com/place/1433019367</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3466,25 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>손톱깎끼</t>
+          <t>네일연다</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>juiceworld_@naver.com</t>
+          <t>jihee335@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1335-1045</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 청학로 86</t>
+          <t>부산광역시 중구 중구로 64-1 2층, 대청동 사거리에서 중구청올라가는 방향으로 올라오시면 있습니다.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailyeonda/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3494,7 +3482,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3515,17 +3503,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3522,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1961112938</t>
+          <t>1797651999</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961112938</t>
+          <t>https://m.place.naver.com/place/1797651999</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3556,39 +3544,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>콩네일</t>
+          <t>민네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lucia_1010@naver.com</t>
+          <t>cej909@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1489-9040</t>
+          <t>0507-1432-9337</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로40번길 8 1층 102호</t>
+          <t>부산광역시 영도구 절영로 531 우리마트&amp;호박터 4층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_sGMan/friend</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3604,22 +3592,22 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>217</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3616,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1098435819</t>
+          <t>1132328251</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098435819</t>
+          <t>https://m.place.naver.com/place/1132328251</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3650,24 +3638,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>니손내손</t>
+          <t>J.Hoo nail</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gusalsv3v@naver.com</t>
+          <t>jhee518_@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1406-4146</t>
+          <t>0507-1484-1180</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 85-1 1층</t>
+          <t>부산광역시 남구 용호로216번길 9 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3707,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3710,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1044585254</t>
+          <t>2076317057</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044585254</t>
+          <t>https://m.place.naver.com/place/2076317057</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3744,24 +3732,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>쿠키네일</t>
+          <t>윤네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>b1758@naver.com</t>
+          <t>yungreem04@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>051-418-2939</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로14번길 28</t>
+          <t>부산광역시 영도구 남항시장길 362</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3801,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3800,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1954239361</t>
+          <t>1213572062</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954239361</t>
+          <t>https://m.place.naver.com/place/1213572062</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3822,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일에스와이</t>
+          <t>네일이떼</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kcjhad109214@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3851,12 +3835,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 향토길 1</t>
+          <t>부산광역시 영도구 웃서발로 9 피아노하우스 1층 101호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_itte</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3866,7 +3850,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3887,17 +3871,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,17 +3890,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1201816037</t>
+          <t>1456764980</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1201816037</t>
+          <t>https://m.place.naver.com/place/1456764980</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3928,34 +3912,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>성은뷰티</t>
+          <t>매니의네일스쿨</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>binsideph_sungeun@naver.com</t>
+          <t>famale@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>051-5556-2115</t>
+          <t>0507-1303-9453</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 17 장메디칼 빌딩 1층</t>
+          <t>부산광역시 중구 대청로 142 2층 매니의네일스쿨</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/me/sebeauty</t>
+          <t>https://blog.naver.com/famale</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3965,7 +3949,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3976,22 +3960,22 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,17 +3984,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1466839388</t>
+          <t>1855010085</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466839388</t>
+          <t>https://m.place.naver.com/place/1855010085</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4006,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>오늘,네일</t>
+          <t>도치네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>isj3333@naver.com</t>
+          <t>multumnonmulta@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -4035,12 +4019,12 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로 15 1층</t>
+          <t>부산광역시 중구 초량중로 3 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/2day__nail</t>
+          <t>https://www.instagram.com/dochi_nail/profilecard/?igsh=cDh6aWI2eGZuOTdp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4066,7 +4050,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4075,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>413</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1924350921</t>
+          <t>1911971963</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924350921</t>
+          <t>https://m.place.naver.com/place/1911971963</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4112,29 +4096,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>오몽네일</t>
+          <t>네일 혠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>olmang_nail@naver.com</t>
+          <t>s2_hennn@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1351-4790</t>
+          <t>0507-1465-0096</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 31 2층</t>
+          <t>부산광역시 영도구 태종로 308 1층 네일혠</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olmang_nail</t>
+          <t>https://instagram.com/nailhyen_?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4149,7 +4133,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4169,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>524</v>
+        <v>43</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>548</v>
+        <v>44</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,17 +4168,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1539347427</t>
+          <t>1733475692</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539347427</t>
+          <t>https://m.place.naver.com/place/1733475692</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4206,34 +4190,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에스더</t>
+          <t>다미네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>estheryoo5@naver.com</t>
+          <t>290eun@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1396-7919</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 260 101호 상가1층(신도브래뉴아파트상가)</t>
+          <t>부산광역시 영도구 산업로 12 2층 다미네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s.the_nail</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4243,7 +4223,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4263,13 +4243,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,17 +4258,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1296125665</t>
+          <t>1919368736</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296125665</t>
+          <t>https://m.place.naver.com/place/1919368736</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4300,24 +4280,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>신디네일</t>
+          <t>섬섬옥수</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>zmfltmvlfhf2@naver.com</t>
+          <t>hohaho1541@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1307-0292</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 상리로 25 동삼그린힐아파트상가 가동 105호</t>
+          <t>부산광역시 동구 중앙대로 210 부산역2F</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4360,10 +4336,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4348,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1341782378</t>
+          <t>1290753909</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1341782378</t>
+          <t>https://m.place.naver.com/place/1290753909</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4394,44 +4370,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>넌네일</t>
+          <t>니손내손</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>vinayav@naver.com</t>
+          <t>gusalsv3v@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1317-2372</t>
+          <t>0507-1406-4146</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 365 (청학동) 1층 넌네일</t>
+          <t>부산광역시 중구 대청로 85-1 1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/nunnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4447,17 +4423,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4442,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2049417397</t>
+          <t>1044585254</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049417397</t>
+          <t>https://m.place.naver.com/place/1044585254</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4488,25 +4464,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일이떼</t>
+          <t>네일제이</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>babastu@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1319-3446</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 웃서발로 9 피아노하우스 1층 101호</t>
+          <t>부산광역시 중구 광복로55번길 14 1층 네일제이</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_itte</t>
+          <t>https://open.kakao.com/o/sHHXqej</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4532,7 +4512,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4541,13 +4521,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4536,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1456764980</t>
+          <t>16430457</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456764980</t>
+          <t>https://m.place.naver.com/place/16430457</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4578,29 +4558,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일엠</t>
+          <t>현네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kkimyuu@naver.com</t>
+          <t>yimda11@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1332-2366</t>
+          <t>0507-1434-4141</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 125 2층</t>
+          <t>부산광역시 영도구 태종로 98 모닝아일랜드 105호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.b.m</t>
+          <t>https://blog.naver.com/yimda11</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4615,7 +4595,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4635,13 +4615,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>485</v>
+        <v>22</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R45" t="n">
-        <v>489</v>
+        <v>34</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4630,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1433019367</t>
+          <t>35475886</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433019367</t>
+          <t>https://m.place.naver.com/place/35475886</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4672,25 +4652,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>엔피케어 부산남포점</t>
+          <t>네일온나</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>np_care@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1383-4154</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 40 12층 미소안 내부</t>
+          <t>부산광역시 중구 구덕로 51 3층 네일온나</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://youtube.com/@npcare_nampo</t>
+          <t>https://www.instagram.com/nail_on_na/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4705,7 +4689,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4725,13 +4709,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>128</v>
+        <v>377</v>
       </c>
       <c r="Q46" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="R46" t="n">
-        <v>192</v>
+        <v>391</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4724,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1102683835</t>
+          <t>1810946003</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102683835</t>
+          <t>https://m.place.naver.com/place/1810946003</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4762,29 +4746,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일온나</t>
+          <t>가이쌀롱 네일&amp;패디샵</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>dbcom36@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1383-4154</t>
+          <t>0507-1342-9301</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 51 3층 네일온나</t>
+          <t>부산광역시 중구 구덕로 13 (남포동1가21-6) 2층, 가이쌀롱</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_on_na/</t>
+          <t>http://instagram.com/gai_salon_</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4819,13 +4803,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>376</v>
+        <v>101</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="R47" t="n">
-        <v>389</v>
+        <v>122</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4818,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1810946003</t>
+          <t>1335843653</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810946003</t>
+          <t>https://m.place.naver.com/place/1335843653</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4856,30 +4840,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>도치네일</t>
+          <t>성은뷰티</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>multumnonmulta@naver.com</t>
+          <t>lse1993@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>051-5556-2115</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 중구 초량중로 3 1층</t>
+          <t>부산광역시 영도구 동삼로 17 장메디칼 빌딩 1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dochi_nail/profilecard/?igsh=cDh6aWI2eGZuOTdp</t>
+          <t>https://open.kakao.com/me/sebeauty</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4905,17 +4893,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,17 +4912,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1911971963</t>
+          <t>1466839388</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911971963</t>
+          <t>https://m.place.naver.com/place/1466839388</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4946,29 +4934,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일하리</t>
+          <t>엔피케어 부산남포점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fromantic@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1464-4548</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼오션로 30 213호</t>
+          <t>부산광역시 중구 구덕로 40 12층 미소안 내부</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@npcare_nampo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4978,12 +4962,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4999,17 +4983,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R49" t="n">
-        <v>5</v>
+        <v>192</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,17 +5002,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1707859953</t>
+          <t>1102683835</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707859953</t>
+          <t>https://m.place.naver.com/place/1102683835</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5040,29 +5024,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>미쯔네일</t>
+          <t>쏘블링네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mizz_nail@naver.com</t>
+          <t>gml94@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1388-3448</t>
+          <t>0507-1367-1696</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로 47-1 3층</t>
+          <t>부산광역시 중구 흑교로 83-1 3층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mizz_nail</t>
+          <t>https://www.instagram.com/sso_blingnail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5077,7 +5061,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5097,13 +5081,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R50" t="n">
-        <v>84</v>
+        <v>670</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5112,17 +5096,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1942024821</t>
+          <t>1946317931</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942024821</t>
+          <t>https://m.place.naver.com/place/1946317931</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5134,25 +5118,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>모던네일</t>
+          <t>네일포시즌 레푸스 남포점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>modern_nail@naver.com</t>
+          <t>mimongmnn@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1498-2303</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 영선대로 81 1층</t>
+          <t>부산광역시 중구 구덕로 50-1 5층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcjxgPG</t>
+          <t>https://litt.ly/refuss_nail4season_busan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5178,7 +5166,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5187,13 +5175,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>1014</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5190,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1428351678</t>
+          <t>1703326180</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428351678</t>
+          <t>https://m.place.naver.com/place/1703326180</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5224,29 +5212,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>J.Hoo nail</t>
+          <t>르메드</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>limnsong@naver.com</t>
+          <t>yellowfox04@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1484-1180</t>
+          <t>051-417-8046</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용호로216번길 9 1층</t>
+          <t>부산광역시 영도구 절영로13번길 5 1층 RE:MADE 르메드</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/re_made.nail</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5256,7 +5244,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5277,17 +5265,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,17 +5284,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2076317057</t>
+          <t>1237521512</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076317057</t>
+          <t>https://m.place.naver.com/place/1237521512</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5306,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>스튜디오뭍</t>
+          <t>뷰티네일샵</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>yein6507@naver.com</t>
+          <t>ofoiaa@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -5331,12 +5319,12 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 97-2 3층</t>
+          <t>부산광역시 영도구 청학북로 21 (청학동) 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/m.u.u.t_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5346,7 +5334,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5367,17 +5355,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5386,17 +5374,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1912631215</t>
+          <t>1501291375</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912631215</t>
+          <t>https://m.place.naver.com/place/1501291375</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5408,34 +5396,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일제이</t>
+          <t>달리뷰띠끄</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>babastu@naver.com</t>
+          <t>sonmh1122@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1319-3446</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로55번길 14 1층 네일제이</t>
+          <t>부산광역시 중구 구덕로 54-1 2층 203호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHHXqej</t>
+          <t>http://pf.kakao.com/_xnYigT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5465,13 +5449,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>17</v>
+        <v>4157</v>
       </c>
       <c r="Q54" t="n">
-        <v>169</v>
+        <v>395</v>
       </c>
       <c r="R54" t="n">
-        <v>186</v>
+        <v>4552</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5480,17 +5464,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>16430457</t>
+          <t>1025786243</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16430457</t>
+          <t>https://m.place.naver.com/place/1025786243</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5502,29 +5486,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>매니의네일스쿨</t>
+          <t>네일에비뉴</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>famale@naver.com</t>
+          <t>sk8ergirl88@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1303-9453</t>
+          <t>0507-1324-6942</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 142 2층 매니의네일스쿨</t>
+          <t>부산광역시 중구 구덕로48번길 3 1층 네일에비뉴</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/famale</t>
+          <t>https://www.instagram.com/nail_auenue86/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5539,7 +5523,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5559,13 +5543,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="R55" t="n">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,17 +5558,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1855010085</t>
+          <t>1865318390</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855010085</t>
+          <t>https://m.place.naver.com/place/1865318390</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5596,25 +5580,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>윤네일</t>
+          <t>제이민뷰티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>yungreem04@naver.com</t>
+          <t>praisingcm@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1414-3834</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항시장길 362</t>
+          <t>부산광역시 중구 해관로 47-1 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://네일인스타https//instagram.com/j_min_nail?igshid=rr24r0p8o90u</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5624,7 +5612,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5645,17 +5633,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5652,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1213572062</t>
+          <t>269796361</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213572062</t>
+          <t>https://m.place.naver.com/place/269796361</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5686,25 +5674,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>뷰티네일샵</t>
+          <t>루네일공방</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ofoiaa@naver.com</t>
+          <t>loonails@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1421-4101</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 청학북로 21 (청학동) 1층</t>
+          <t>부산광역시 중구 광복중앙로 3 루네일공방 1층 (창선파출소 옆골목)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/loonailsfactory</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5714,7 +5706,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5735,17 +5727,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5754,17 +5746,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1501291375</t>
+          <t>37484954</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501291375</t>
+          <t>https://m.place.naver.com/place/37484954</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5776,30 +5768,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>다미네일</t>
+          <t>네일살롱 문</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>wngml1492@naver.com</t>
+          <t>95thvldk@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1367-6993</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 산업로 12 2층 다미네일</t>
+          <t>부산광역시 남구 동명로152번길 93 용호시장 1층 20호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://www.instagram.com/nail_salon_moon</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5809,7 +5805,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5829,13 +5825,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5844,17 +5840,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1919368736</t>
+          <t>1688553170</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919368736</t>
+          <t>https://m.place.naver.com/place/1688553170</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5866,25 +5862,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일하고가</t>
+          <t>신디네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>fromantic@naver.com</t>
+          <t>zmfltmvlfhf2@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1307-0292</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 중구 해관로 3 1층</t>
+          <t>부산광역시 영도구 상리로 25 동삼그린힐아파트상가 가동 105호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhagoga/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5915,17 +5915,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5934,17 +5934,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2030742681</t>
+          <t>1341782378</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030742681</t>
+          <t>https://m.place.naver.com/place/1341782378</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5956,34 +5956,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일&amp;속눈썹 마찝</t>
+          <t>더블랙뷰티 부민점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hanna6883@naver.com</t>
+          <t>theblackbeauty@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>051-711-1101</t>
+          <t>0507-1376-5423</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 웃서발로 86 1층</t>
+          <t>부산광역시 서구 구덕로 214 3층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sR6gMBue</t>
+          <t>http://pf.kakao.com/_FyFcn</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="Q60" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>308</v>
+        <v>125</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6028,17 +6028,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1958309487</t>
+          <t>2002868588</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958309487</t>
+          <t>https://m.place.naver.com/place/2002868588</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6050,29 +6050,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>눈네일</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yunimil@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1350-2086</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 중구 해관로 22-1 3층</t>
+          <t>부산광역시 중구 흑교로75번길 4-2 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noonnail</t>
+          <t>https://www.instagram.com/momonail0077</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6098,7 +6094,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6107,13 +6103,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="R61" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6122,17 +6118,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1509715865</t>
+          <t>1050708757</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509715865</t>
+          <t>https://m.place.naver.com/place/1050708757</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6144,39 +6140,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>푸스케어 남포점 글림네일</t>
+          <t>단비네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mcnampo@naver.com</t>
+          <t>danb38@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1331-8813</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 32-1 3층</t>
+          <t>부산광역시 영도구 해안산책길 20</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://typebot.co/fusscarenampo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6197,17 +6189,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>298</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>607</v>
+        <v>7</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6216,17 +6208,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1305002599</t>
+          <t>1536793796</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1305002599</t>
+          <t>https://m.place.naver.com/place/1536793796</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6238,30 +6230,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LOVEMINNAIL</t>
+          <t>네일타임즈 부산 송도 해수욕장점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cordelia0211@naver.com</t>
+          <t>rina_story1@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1491-4424</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 서구 구덕로 230-1 에머글링 커피숍 2층</t>
+          <t>부산광역시 서구 등대로 9 송도유림스카이오션더퍼스트 3층 306호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/loveminnail</t>
+          <t>https://pf.kakao.com/_PxbSxhn</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6282,7 +6278,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6291,13 +6287,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="Q63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6306,17 +6302,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1098467582</t>
+          <t>1667862272</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098467582</t>
+          <t>https://m.place.naver.com/place/1667862272</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6328,29 +6324,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에스타네일 남포점</t>
+          <t>에스더</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hoihoi1704@naver.com</t>
+          <t>estheryoo5@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1367-1210</t>
+          <t>0507-1396-7919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로 45-12 에스타네일</t>
+          <t>부산광역시 영도구 태종로 260 101호 상가1층(신도브래뉴아파트상가)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/estarnail_</t>
+          <t>https://www.instagram.com/s.the_nail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6385,13 +6381,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6400,17 +6396,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1193980987</t>
+          <t>1296125665</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193980987</t>
+          <t>https://m.place.naver.com/place/1296125665</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6422,25 +6418,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>섬섬옥수</t>
+          <t>치코네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ulju_love@naver.com</t>
+          <t>ddo_18@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1379-7941</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 동구 중앙대로 210 부산역2F</t>
+          <t>부산광역시 남구 용호로216번가길 23 미광빌딩 1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/chico_nail_?igsh=a2R0cXJ4YmUyMHRs&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6471,17 +6471,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6490,17 +6490,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1290753909</t>
+          <t>37565672</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290753909</t>
+          <t>https://m.place.naver.com/place/37565672</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6512,29 +6512,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일 혠</t>
+          <t>다듬다</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>s2_hennn@naver.com</t>
+          <t>areumkor@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1465-0096</t>
+          <t>0507-1444-1139</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 308 1층 네일혠</t>
+          <t>부산광역시 중구 대청로 57 다듬다2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailhyen_?utm_medium=copy_link</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6584,17 +6584,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1733475692</t>
+          <t>1282118461</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1733475692</t>
+          <t>https://m.place.naver.com/place/1282118461</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6606,20 +6606,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>단비네일</t>
+          <t>콩네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>danb38@naver.com</t>
+          <t>lucia_1010@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1489-9040</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 해안산책길 20</t>
+          <t>부산광역시 영도구 대교로40번길 8 1층 102호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6659,13 +6663,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6674,17 +6678,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1536793796</t>
+          <t>1098435819</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1536793796</t>
+          <t>https://m.place.naver.com/place/1098435819</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6696,29 +6700,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>다듬다</t>
+          <t>스튜디오뭍</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>areumkor@naver.com</t>
+          <t>yein6507@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1444-1139</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 57 다듬다2층</t>
+          <t>부산광역시 중구 대청로 97-2 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/m.u.u.t_</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>36</v>
+        <v>312</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>40</v>
+        <v>317</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6768,17 +6768,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1282118461</t>
+          <t>1912631215</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282118461</t>
+          <t>https://m.place.naver.com/place/1912631215</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6790,29 +6790,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>썬 네일</t>
+          <t>네일하고가</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sunnail3024@naver.com</t>
+          <t>fromantic@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1341-0099</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용주로 23 1층</t>
+          <t>부산광역시 중구 해관로 3 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailhagoga/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6822,7 +6818,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6843,17 +6839,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6862,17 +6858,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1900035133</t>
+          <t>2030742681</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1900035133</t>
+          <t>https://m.place.naver.com/place/2030742681</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6884,40 +6880,44 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>솔네일</t>
+          <t>넌네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ioio93@naver.com</t>
+          <t>qweertyu1@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1317-2372</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 422 태림맨션상가 103호</t>
+          <t>부산광역시 영도구 태종로 365 (청학동) 1층 넌네일</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/nunnail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6933,17 +6933,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6952,17 +6952,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1216411669</t>
+          <t>2049417397</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216411669</t>
+          <t>https://m.place.naver.com/place/2049417397</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6974,44 +6974,44 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>설탕네일</t>
+          <t>손꽃풀네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sos0902kr@naver.com</t>
+          <t>bongjuyha@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1400-2205</t>
+          <t>0507-1348-6215</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로29번길 55 설탕네일</t>
+          <t>부산광역시 영도구 동삼로 72 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://toss-order.tossplace.com/booking/vfSz8GDhgdoBPnv</t>
+          <t>https://blog.naver.com/bongjuyha</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7031,13 +7031,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7046,17 +7046,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1391812097</t>
+          <t>1289134648</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391812097</t>
+          <t>https://m.place.naver.com/place/1289134648</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7068,29 +7068,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>현네일</t>
+          <t>뽀시락네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>yimda11@naver.com</t>
+          <t>yujin1430@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1434-4141</t>
+          <t>0507-1350-2309</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 98 모닝아일랜드 105호</t>
+          <t>부산광역시 영도구 대교로14번길 21-4 1층 뽀시락네일</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yimda11</t>
+          <t>https://open.kakao.com/o/s1WfpFWd</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7116,22 +7116,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7140,17 +7140,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>35475886</t>
+          <t>1347303952</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35475886</t>
+          <t>https://m.place.naver.com/place/1347303952</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7162,29 +7162,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일살롱 문</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>95thvldk@naver.com</t>
-        </is>
-      </c>
+          <t>손톱</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1367-6993</t>
+          <t>070-8882-4003</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 남구 동명로152번길 93 용호시장 1층 20호</t>
+          <t>부산광역시 영도구 조내기로 38-1 원우엔리치빌상가 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_salon_moon</t>
+          <t>https://www.instagram.com/nail_young4003</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7219,13 +7215,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="Q73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>155</v>
+        <v>50</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7234,17 +7230,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1688553170</t>
+          <t>1299202573</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688553170</t>
+          <t>https://m.place.naver.com/place/1299202573</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7256,34 +7252,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일타임즈 부산 송도 해수욕장점</t>
+          <t>The GRIDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rina_story1@naver.com</t>
+          <t>the-grida@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1491-4424</t>
+          <t>0507-1393-7300</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 서구 등대로 9 송도유림스카이오션더퍼스트 3층 306호</t>
+          <t>부산광역시 중구 중구로 22 창선상가1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_PxbSxhn</t>
+          <t>https://blog.naver.com/the-grida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7293,7 +7289,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7304,22 +7300,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7328,17 +7324,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1667862272</t>
+          <t>1992166482</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667862272</t>
+          <t>https://m.place.naver.com/place/1992166482</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7350,29 +7346,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>뽀시락네일</t>
+          <t>윤아네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>yujin1430@naver.com</t>
+          <t>gmlwjd1902@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1350-2309</t>
+          <t>0507-1322-6563</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로14번길 21-4 1층 뽀시락네일</t>
+          <t>부산광역시 영도구 절영로 504 상가 206호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1WfpFWd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7382,7 +7378,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7398,7 +7394,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7410,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7422,17 +7418,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1347303952</t>
+          <t>1363399967</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347303952</t>
+          <t>https://m.place.naver.com/place/1363399967</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7444,29 +7440,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일에비뉴</t>
+          <t>눈네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>seoinyoung@naver.com</t>
+          <t>yunimil@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1324-6942</t>
+          <t>0507-1350-2086</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로48번길 3 1층 네일에비뉴</t>
+          <t>부산광역시 중구 해관로 22-1 3층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_auenue86/</t>
+          <t>https://www.instagram.com/noonnail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7492,7 +7488,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7501,13 +7497,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>227</v>
+        <v>9</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R76" t="n">
-        <v>230</v>
+        <v>17</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7516,17 +7512,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1865318390</t>
+          <t>1509715865</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865318390</t>
+          <t>https://m.place.naver.com/place/1509715865</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/영도구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/영도구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>손이예쁜그녀</t>
+          <t>네일엠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nail_won@naver.com</t>
+          <t>kkimyuu@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>051-404-4141</t>
+          <t>0507-1332-2366</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 89 손이예쁜그녀</t>
+          <t>부산광역시 중구 대청로 125 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailjiwon</t>
+          <t>https://www.instagram.com/nail.b.m</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>487</v>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>165</v>
+        <v>491</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>36636875</t>
+          <t>1433019367</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36636875</t>
+          <t>https://m.place.naver.com/place/1433019367</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,39 +658,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>남포동네일옐로</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>suhyun5618@naver.com</t>
-        </is>
-      </c>
+          <t>민네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1378-0493</t>
+          <t>0507-1432-9337</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 중구 남포동1가 11 41호</t>
+          <t>부산광역시 영도구 절영로 531 우리마트&amp;호박터 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_sGMan/friend</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -706,22 +702,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>217</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>324</v>
+        <v>240</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1003177563</t>
+          <t>1132328251</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003177563</t>
+          <t>https://m.place.naver.com/place/1132328251</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,25 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>솔네일</t>
+          <t>뷰티3975</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ioio93@naver.com</t>
+          <t>chdbs0968@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1373-0968</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 422 태림맨션상가 103호</t>
+          <t>부산광역시 중구 광복로55번길 1-1 2. 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/chdbs0968</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>862</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>1027</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1216411669</t>
+          <t>1165703720</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216411669</t>
+          <t>https://m.place.naver.com/place/1165703720</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -842,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마벨네일뷰티남포</t>
+          <t>눈네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tiia@naver.com</t>
+          <t>yunimil@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1344-0730</t>
+          <t>0507-1350-2086</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 중구 남포길 28-1 3층 마벨네일뷰티</t>
+          <t>부산광역시 중구 해관로 22-1 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ma.belle_nail</t>
+          <t>https://www.instagram.com/noonnail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1631435764</t>
+          <t>1509715865</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631435764</t>
+          <t>https://m.place.naver.com/place/1509715865</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -936,25 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포유네일</t>
+          <t>손꽃풀네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nail_for_u@naver.com</t>
+          <t>bongjuyha@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1348-6215</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 56 한나타워 3층</t>
+          <t>부산광역시 영도구 동삼로 72 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bongjuyha</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -964,12 +968,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -985,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>149</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>16383416</t>
+          <t>1289134648</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16383416</t>
+          <t>https://m.place.naver.com/place/1289134648</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1030,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뷰티3975</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>chdbs0968@naver.com</t>
-        </is>
-      </c>
+          <t>가이쌀롱 네일&amp;패디샵</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1373-0968</t>
+          <t>0507-1342-9301</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로55번길 1-1 2. 3층</t>
+          <t>부산광역시 중구 구덕로 13 (남포동1가21-6) 2층, 가이쌀롱</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chdbs0968</t>
+          <t>http://instagram.com/gai_salon_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>858</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="n">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
-        <v>1023</v>
+        <v>123</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1165703720</t>
+          <t>1335843653</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165703720</t>
+          <t>https://m.place.naver.com/place/1335843653</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1120,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일하리</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>nobleliz_@naver.com</t>
-        </is>
-      </c>
+          <t>단비네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1464-4548</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼오션로 30 213호</t>
+          <t>부산광역시 영도구 해안산책길 20</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1707859953</t>
+          <t>1536793796</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707859953</t>
+          <t>https://m.place.naver.com/place/1536793796</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,20 +1206,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일에스와이</t>
+          <t>남포동네일옐로</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcjhad109214@naver.com</t>
+          <t>suhyun5618@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1378-0493</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 향토길 1</t>
+          <t>부산광역시 중구 남포동1가 11 41호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1267,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1201816037</t>
+          <t>1003177563</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1201816037</t>
+          <t>https://m.place.naver.com/place/1003177563</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1304,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>손톱이야기</t>
+          <t>마벨네일뷰티남포</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rexdialeon@naver.com</t>
+          <t>tiia@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>051-417-7005</t>
+          <t>0507-1344-0730</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로101번길 38</t>
+          <t>부산광역시 중구 남포길 28-1 3층 마벨네일뷰티</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_ma.belle_nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1336,7 +1332,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1352,22 +1348,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36925644</t>
+          <t>1631435764</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36925644</t>
+          <t>https://m.place.naver.com/place/1631435764</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1398,34 +1394,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>미소샵네일</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ehdkdlahd@naver.com</t>
-        </is>
-      </c>
+          <t>달리뷰띠끄</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1338-7038</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중앙대로 45 3층 301호</t>
+          <t>부산광역시 중구 구덕로 54-1 2층 203호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehdkdlahd</t>
+          <t>http://pf.kakao.com/_xnYigT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1435,7 +1423,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1446,7 +1434,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1455,13 +1443,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>113</v>
+        <v>4159</v>
       </c>
       <c r="Q11" t="n">
-        <v>499</v>
+        <v>395</v>
       </c>
       <c r="R11" t="n">
-        <v>612</v>
+        <v>4554</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1458,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1824109129</t>
+          <t>1025786243</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824109129</t>
+          <t>https://m.place.naver.com/place/1025786243</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1480,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오몽네일</t>
+          <t>뷰티데이</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>olmang_nail@naver.com</t>
+          <t>1208_sj@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1351-4790</t>
+          <t>0507-1369-7116</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 31 2층</t>
+          <t>부산광역시 중구 구덕로 12-1 도시철도 남포역 지하상가 21호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/olmang_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1524,12 +1512,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1545,17 +1533,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>522</v>
+        <v>128</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>546</v>
+        <v>129</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1552,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1539347427</t>
+          <t>2080886215</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539347427</t>
+          <t>https://m.place.naver.com/place/2080886215</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1586,21 +1574,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>모던네일</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>넌네일</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>vinayav@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1317-2372</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 영선대로 81 1층</t>
+          <t>부산광역시 영도구 태종로 365 (청학동) 1층 넌네일</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcjxgPG</t>
+          <t>https://link.inpock.co.kr/nunnail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1615,7 +1611,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1626,7 +1622,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1638,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1646,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1428351678</t>
+          <t>2049417397</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428351678</t>
+          <t>https://m.place.naver.com/place/2049417397</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1672,29 +1668,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기분전환네일</t>
+          <t>아르떼살롱</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jisoo851208@naver.com</t>
+          <t>dnflaowja@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1368-1158</t>
+          <t>0507-1329-0048</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼북로 20 일동미라주브라이튼 1단지 상가 110호</t>
+          <t>부산광역시 동구 중앙대로 181 3층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/gbjh_nail</t>
+          <t>http://instagram.com/_arte_salon</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1729,13 +1725,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="Q14" t="n">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>349</v>
+        <v>122</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>53146158</t>
+          <t>1914602054</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/53146158</t>
+          <t>https://m.place.naver.com/place/1914602054</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1766,44 +1762,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>미쯔네일</t>
+          <t>설탕네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mizz_nail@naver.com</t>
+          <t>sos0902kr@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1388-3448</t>
+          <t>0507-1400-2205</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로 47-1 3층</t>
+          <t>부산광역시 영도구 절영로29번길 55 설탕네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mizz_nail</t>
+          <t>https://toss-order.tossplace.com/booking/vfSz8GDhgdoBPnv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1823,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1942024821</t>
+          <t>1391812097</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942024821</t>
+          <t>https://m.place.naver.com/place/1391812097</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1860,29 +1856,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>썬 네일</t>
+          <t>네일제이</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sunnail3024@naver.com</t>
+          <t>babastu@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1341-0099</t>
+          <t>0507-1319-3446</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용주로 23 1층</t>
+          <t>부산광역시 중구 광복로55번길 14 1층 네일제이</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sHHXqej</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1892,7 +1888,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1908,22 +1904,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="R16" t="n">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1900035133</t>
+          <t>16430457</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1900035133</t>
+          <t>https://m.place.naver.com/place/16430457</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1954,24 +1950,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>쿠키네일</t>
+          <t>네일하리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>gksrhdwn0804@naver.com</t>
+          <t>fromantic@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>051-418-2939</t>
+          <t>0507-1464-4548</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로14번길 28</t>
+          <t>부산광역시 영도구 동삼오션로 30 213호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2011,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2026,51 +2022,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1954239361</t>
+          <t>1707859953</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954239361</t>
+          <t>https://m.place.naver.com/place/1707859953</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>속눈썹증모,연장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>푸스케어 남포점 글림네일</t>
+          <t>눈썹살롱 네일살롱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mcnampo@naver.com</t>
+          <t>sallyjuli@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1331-8813</t>
+          <t>0507-1375-4952</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 32-1 3층</t>
+          <t>부산광역시 영도구 남항로49번길 52 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://typebot.co/fusscarenampo</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2080,7 +2076,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2105,13 +2101,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>299</v>
+        <v>31</v>
       </c>
       <c r="Q18" t="n">
-        <v>309</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>608</v>
+        <v>32</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2120,17 +2116,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1305002599</t>
+          <t>1925879465</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1305002599</t>
+          <t>https://m.place.naver.com/place/1925879465</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2142,39 +2138,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>설탕네일</t>
+          <t>르메드</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sos0902kr@naver.com</t>
+          <t>yellowfox04@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1400-2205</t>
+          <t>051-417-8046</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로29번길 55 설탕네일</t>
+          <t>부산광역시 영도구 절영로13번길 5 1층 RE:MADE 르메드</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://toss-order.tossplace.com/booking/vfSz8GDhgdoBPnv</t>
+          <t>https://www.instagram.com/re_made.nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2199,13 +2195,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2214,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1391812097</t>
+          <t>1237521512</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391812097</t>
+          <t>https://m.place.naver.com/place/1237521512</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2236,25 +2232,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>오늘,네일</t>
+          <t>에스더</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bb_syun126@naver.com</t>
+          <t>estheryoo5@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1396-7919</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로 15 1층</t>
+          <t>부산광역시 영도구 태종로 260 101호 상가1층(신도브래뉴아파트상가)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/2day__nail</t>
+          <t>https://www.instagram.com/s.the_nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
         <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2304,17 +2304,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1924350921</t>
+          <t>1296125665</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924350921</t>
+          <t>https://m.place.naver.com/place/1296125665</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2326,39 +2326,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일앤블랑</t>
+          <t>신디네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rang-design@naver.com</t>
+          <t>zmfltmvlfhf2@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1398-7040</t>
+          <t>0507-1307-0292</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로34번길 7 세컨페이스 4층</t>
+          <t>부산광역시 영도구 상리로 25 동삼그린힐아파트상가 가동 105호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnGftxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2374,22 +2374,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2398,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1479860666</t>
+          <t>1341782378</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479860666</t>
+          <t>https://m.place.naver.com/place/1341782378</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2420,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>쁨잇</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>qpt1107@naver.com</t>
-        </is>
-      </c>
+          <t>제이민뷰티</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1480-4861</t>
+          <t>0507-1414-3834</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로 34 2층</t>
+          <t>부산광역시 중구 해관로 47-1 2층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ppeumit_nail</t>
+          <t>http://네일인스타https//instagram.com/j_min_nail?igshid=rr24r0p8o90u</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,13 +2473,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2488,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1931140160</t>
+          <t>269796361</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931140160</t>
+          <t>https://m.place.naver.com/place/269796361</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2514,29 +2510,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>나나뷰티살롱</t>
+          <t>네일에비뉴</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rosyn_@naver.com</t>
+          <t>seoinyoung@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1336-2115</t>
+          <t>0507-1324-6942</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 557 삼창파크맨션 상가101호</t>
+          <t>부산광역시 중구 구덕로48번길 3 1층 네일에비뉴</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nana2115__</t>
+          <t>https://www.instagram.com/nail_auenue86/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2562,7 +2558,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2571,13 +2567,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="Q23" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>112</v>
+        <v>230</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2586,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1829607863</t>
+          <t>1865318390</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1829607863</t>
+          <t>https://m.place.naver.com/place/1865318390</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2608,29 +2604,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일반하다</t>
+          <t>도치네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>iiijuheeiii@naver.com</t>
+          <t>multumnonmulta@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>051-915-7022</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로 18-1</t>
+          <t>부산광역시 중구 초량중로 3 1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://instagram.com/banhada_nail_</t>
+          <t>https://www.instagram.com/dochi_nail/profilecard/?igsh=cDh6aWI2eGZuOTdp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2656,7 +2648,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2665,13 +2657,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>399</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R24" t="n">
-        <v>23</v>
+        <v>415</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2680,17 +2672,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>572364787</t>
+          <t>1911971963</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/572364787</t>
+          <t>https://m.place.naver.com/place/1911971963</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2702,25 +2694,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손톱깎끼</t>
+          <t>기분전환네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dojin4538@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1368-1158</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 청학로 86</t>
+          <t>부산광역시 영도구 동삼북로 20 일동미라주브라이튼 1단지 상가 110호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/gbjh_nail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2730,7 +2726,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2751,17 +2747,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,17 +2766,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1961112938</t>
+          <t>53146158</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961112938</t>
+          <t>https://m.place.naver.com/place/53146158</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2792,29 +2788,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스타네일 남포점</t>
+          <t>포유네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hoihoi1704@naver.com</t>
+          <t>nail_for_u@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1367-1210</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로 45-12 에스타네일</t>
+          <t>부산광역시 영도구 동삼로 56 한나타워 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/estarnail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2824,7 +2816,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2845,17 +2837,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>236</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>243</v>
+        <v>4</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2856,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1193980987</t>
+          <t>16383416</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193980987</t>
+          <t>https://m.place.naver.com/place/16383416</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2878,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일&amp;속눈썹 마찝</t>
+          <t>매니의네일스쿨</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>hanna6883@naver.com</t>
+          <t>famale@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>051-711-1101</t>
+          <t>0507-1303-9453</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 웃서발로 86 1층</t>
+          <t>부산광역시 중구 대청로 142 2층 매니의네일스쿨</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sR6gMBue</t>
+          <t>https://blog.naver.com/famale</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2923,7 +2915,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2934,7 +2926,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2943,13 +2935,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>238</v>
+        <v>62</v>
       </c>
       <c r="Q27" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="R27" t="n">
-        <v>308</v>
+        <v>94</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2958,17 +2950,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1958309487</t>
+          <t>1855010085</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958309487</t>
+          <t>https://m.place.naver.com/place/1855010085</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2980,29 +2972,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아르떼살롱</t>
+          <t>미소샵네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dnflaowja@naver.com</t>
+          <t>ehdkdlahd@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1329-0048</t>
+          <t>0507-1338-7038</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 동구 중앙대로 181 3층</t>
+          <t>부산광역시 중구 중앙대로 45 3층 301호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://instagram.com/_arte_salon</t>
+          <t>https://blog.naver.com/ehdkdlahd</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3017,7 +3009,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3037,13 +3029,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>499</v>
       </c>
       <c r="R28" t="n">
-        <v>122</v>
+        <v>612</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,17 +3044,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1914602054</t>
+          <t>1824109129</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914602054</t>
+          <t>https://m.place.naver.com/place/1824109129</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3074,29 +3066,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>뷰티데이</t>
+          <t>에스타네일 남포점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1208_sj@naver.com</t>
+          <t>hoihoi1704@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1369-7116</t>
+          <t>0507-1367-1210</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 12-1 도시철도 남포역 지하상가 21호</t>
+          <t>부산광역시 중구 광복로 45-12 에스타네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/estarnail_</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3106,7 +3098,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3127,17 +3119,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>127</v>
+        <v>236</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,51 +3138,43 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2080886215</t>
+          <t>1193980987</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080886215</t>
+          <t>https://m.place.naver.com/place/1193980987</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>눈썹살롱 네일살롱</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>sallyjuli@naver.com</t>
-        </is>
-      </c>
+          <t>다미네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1375-4952</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로49번길 52 1층</t>
+          <t>부산광역시 영도구 산업로 12 2층 다미네일</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3200,12 +3184,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3225,13 +3209,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3224,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1925879465</t>
+          <t>1919368736</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925879465</t>
+          <t>https://m.place.naver.com/place/1919368736</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3262,34 +3246,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>손톱에 물들다</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>wldms141300@naver.com</t>
-        </is>
-      </c>
+          <t>성은뷰티</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>070-8257-6168</t>
+          <t>051-5556-2115</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로292번길 23</t>
+          <t>부산광역시 영도구 동삼로 17 장메디칼 빌딩 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eunjung.c_nail</t>
+          <t>https://open.kakao.com/me/sebeauty</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3310,12 +3290,12 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -3334,17 +3314,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>38262661</t>
+          <t>1466839388</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38262661</t>
+          <t>https://m.place.naver.com/place/1466839388</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3356,29 +3336,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일엠</t>
+          <t>네일연다</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kkimyuu@naver.com</t>
+          <t>jihee335@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1332-2366</t>
+          <t>0507-1335-1045</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 125 2층</t>
+          <t>부산광역시 중구 중구로 64-1 2층, 대청동 사거리에서 중구청올라가는 방향으로 올라오시면 있습니다.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.b.m</t>
+          <t>https://www.instagram.com/nailyeonda/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3413,13 +3393,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>487</v>
+        <v>26</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>491</v>
+        <v>28</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,17 +3408,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1433019367</t>
+          <t>1797651999</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433019367</t>
+          <t>https://m.place.naver.com/place/1797651999</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3450,29 +3430,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일연다</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>jihee335@naver.com</t>
-        </is>
-      </c>
+          <t>쏘블링네일&amp;속눈썹펌</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1335-1045</t>
+          <t>0507-1367-1696</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중구로 64-1 2층, 대청동 사거리에서 중구청올라가는 방향으로 올라오시면 있습니다.</t>
+          <t>부산광역시 중구 흑교로 83-1 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyeonda/</t>
+          <t>https://www.instagram.com/sso_blingnail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3507,13 +3483,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>26</v>
+        <v>657</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
-        <v>28</v>
+        <v>677</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,17 +3498,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1797651999</t>
+          <t>1946317931</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797651999</t>
+          <t>https://m.place.naver.com/place/1946317931</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3544,39 +3520,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>민네일</t>
+          <t>뷰티네일샵</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cej909@naver.com</t>
+          <t>ofoiaa@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1432-9337</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 531 우리마트&amp;호박터 4층</t>
+          <t>부산광역시 영도구 청학북로 21 (청학동) 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sGMan/friend</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3592,22 +3564,22 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3588,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1132328251</t>
+          <t>1501291375</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132328251</t>
+          <t>https://m.place.naver.com/place/1501291375</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3638,29 +3610,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>J.Hoo nail</t>
+          <t>JALHAE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jhee518_@naver.com</t>
+          <t>neona_jalhae@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1484-1180</t>
+          <t>0507-1418-0915</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용호로216번길 9 1층</t>
+          <t>부산광역시 중구 대청로35번길 3 1층 민들레미용실안</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/s5cpdMOh</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3670,7 +3642,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3686,22 +3658,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3682,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2076317057</t>
+          <t>2014599026</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076317057</t>
+          <t>https://m.place.naver.com/place/2014599026</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3732,20 +3704,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>윤네일</t>
+          <t>썬 네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yungreem04@naver.com</t>
+          <t>sunnail3024@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1341-0099</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항시장길 362</t>
+          <t>부산광역시 남구 용주로 23 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3785,13 +3761,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3800,17 +3776,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1213572062</t>
+          <t>1900035133</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213572062</t>
+          <t>https://m.place.naver.com/place/1900035133</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3822,25 +3798,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일이떼</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>daonnail0305@naver.com</t>
-        </is>
-      </c>
+          <t>네일&amp;속눈썹 마찝</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>051-711-1101</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 웃서발로 9 피아노하우스 1층 101호</t>
+          <t>부산광역시 영도구 웃서발로 86 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_itte</t>
+          <t>https://open.kakao.com/o/sR6gMBue</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3866,7 +3842,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3875,13 +3851,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3890,17 +3866,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1456764980</t>
+          <t>1958309487</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456764980</t>
+          <t>https://m.place.naver.com/place/1958309487</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3912,29 +3888,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>매니의네일스쿨</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>famale@naver.com</t>
-        </is>
-      </c>
+          <t>네일에스와이</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1303-9453</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 142 2층 매니의네일스쿨</t>
+          <t>부산광역시 영도구 향토길 1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/famale</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3944,12 +3912,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3965,17 +3933,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +3952,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1855010085</t>
+          <t>1201816037</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855010085</t>
+          <t>https://m.place.naver.com/place/1201816037</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4006,30 +3974,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>도치네일</t>
+          <t>푸스케어 남포점 글림네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>multumnonmulta@naver.com</t>
+          <t>mcnampo@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1331-8813</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 중구 초량중로 3 1층</t>
+          <t>부산광역시 중구 구덕로 32-1 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dochi_nail/profilecard/?igsh=cDh6aWI2eGZuOTdp</t>
+          <t>https://typebot.co/fusscarenampo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4050,7 +4022,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4059,13 +4031,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>397</v>
+        <v>299</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="R39" t="n">
-        <v>413</v>
+        <v>608</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4074,17 +4046,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1911971963</t>
+          <t>1305002599</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911971963</t>
+          <t>https://m.place.naver.com/place/1305002599</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4096,29 +4068,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일 혠</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>s2_hennn@naver.com</t>
-        </is>
-      </c>
+          <t>손톱에 물들다</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1465-0096</t>
+          <t>070-8257-6168</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 308 1층 네일혠</t>
+          <t>부산광역시 영도구 태종로292번길 23</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailhyen_?utm_medium=copy_link</t>
+          <t>https://www.instagram.com/eunjung.c_nail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4153,13 +4121,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4136,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1733475692</t>
+          <t>38262661</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1733475692</t>
+          <t>https://m.place.naver.com/place/38262661</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4190,30 +4158,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>다미네일</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>290eun@naver.com</t>
-        </is>
-      </c>
+          <t>네일 혠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1465-0096</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 산업로 12 2층 다미네일</t>
+          <t>부산광역시 영도구 태종로 308 1층 네일혠</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://instagram.com/nailhyen_?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4223,7 +4191,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4243,13 +4211,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4258,17 +4226,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1919368736</t>
+          <t>1733475692</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919368736</t>
+          <t>https://m.place.naver.com/place/1733475692</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4280,25 +4248,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>섬섬옥수</t>
+          <t>현네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hohaho1541@naver.com</t>
+          <t>yimda11@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1434-4141</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 동구 중앙대로 210 부산역2F</t>
+          <t>부산광역시 영도구 태종로 98 모닝아일랜드 105호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/yimda11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4308,12 +4280,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4329,17 +4301,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R42" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4348,17 +4320,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1290753909</t>
+          <t>35475886</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290753909</t>
+          <t>https://m.place.naver.com/place/35475886</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4370,29 +4342,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>니손내손</t>
+          <t>The GRIDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>gusalsv3v@naver.com</t>
+          <t>the-grida@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1406-4146</t>
+          <t>0507-1393-7300</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 85-1 1층</t>
+          <t>부산광역시 중구 중구로 22 창선상가1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/the-grida</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4402,12 +4374,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4427,13 +4399,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4442,17 +4414,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1044585254</t>
+          <t>1992166482</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044585254</t>
+          <t>https://m.place.naver.com/place/1992166482</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4464,29 +4436,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일제이</t>
+          <t>손이예쁜그녀</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>babastu@naver.com</t>
+          <t>nail_won@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1319-3446</t>
+          <t>051-404-4141</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로55번길 14 1층 네일제이</t>
+          <t>부산광역시 영도구 동삼로 89 손이예쁜그녀</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHHXqej</t>
+          <t>https://www.instagram.com/nailjiwon</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4512,7 +4484,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4521,13 +4493,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="n">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="R44" t="n">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4536,17 +4508,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>16430457</t>
+          <t>36636875</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16430457</t>
+          <t>https://m.place.naver.com/place/36636875</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4558,29 +4530,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>현네일</t>
+          <t>섬섬옥수</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>yimda11@naver.com</t>
+          <t>ekgo5600@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1434-4141</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 98 모닝아일랜드 105호</t>
+          <t>부산광역시 동구 중앙대로 210 부산역2F</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yimda11</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4590,12 +4558,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4611,17 +4579,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R45" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4630,17 +4598,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>35475886</t>
+          <t>1290753909</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35475886</t>
+          <t>https://m.place.naver.com/place/1290753909</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4652,29 +4620,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일온나</t>
+          <t>루네일공방</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>loonails@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1383-4154</t>
+          <t>0507-1421-4101</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 51 3층 네일온나</t>
+          <t>부산광역시 중구 광복중앙로 3 루네일공방 1층 (창선파출소 옆골목)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_on_na/</t>
+          <t>https://www.instagram.com/loonailsfactory</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4709,13 +4677,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>195</v>
       </c>
       <c r="R46" t="n">
-        <v>391</v>
+        <v>504</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4724,17 +4692,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1810946003</t>
+          <t>37484954</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810946003</t>
+          <t>https://m.place.naver.com/place/37484954</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4746,34 +4714,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>가이쌀롱 네일&amp;패디샵</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>dbcom36@naver.com</t>
-        </is>
-      </c>
+          <t>네일앤블랑</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1342-9301</t>
+          <t>0507-1398-7040</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 13 (남포동1가21-6) 2층, 가이쌀롱</t>
+          <t>부산광역시 중구 구덕로34번길 7 세컨페이스 4층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://instagram.com/gai_salon_</t>
+          <t>http://pf.kakao.com/_xnGftxj</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4794,7 +4758,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4803,13 +4767,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="R47" t="n">
-        <v>122</v>
+        <v>219</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4818,17 +4782,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1335843653</t>
+          <t>1479860666</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335843653</t>
+          <t>https://m.place.naver.com/place/1479860666</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4840,39 +4804,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>성은뷰티</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>lse1993@naver.com</t>
-        </is>
-      </c>
+          <t>다듬다</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>051-5556-2115</t>
+          <t>0507-1444-1139</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 17 장메디칼 빌딩 1층</t>
+          <t>부산광역시 중구 대청로 57 다듬다2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/me/sebeauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4888,7 +4848,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4897,13 +4857,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4912,17 +4872,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1466839388</t>
+          <t>1282118461</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466839388</t>
+          <t>https://m.place.naver.com/place/1282118461</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4934,25 +4894,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>엔피케어 부산남포점</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>np_care@naver.com</t>
-        </is>
-      </c>
+          <t>윤네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 40 12층 미소안 내부</t>
+          <t>부산광역시 영도구 남항시장길 362</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://youtube.com/@npcare_nampo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4962,12 +4918,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4983,17 +4939,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>192</v>
+        <v>8</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5002,17 +4958,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1102683835</t>
+          <t>1213572062</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102683835</t>
+          <t>https://m.place.naver.com/place/1213572062</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5024,29 +4980,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>쏘블링네일</t>
+          <t>네일하고가</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>gml94@naver.com</t>
+          <t>fromantic@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1367-1696</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 중구 흑교로 83-1 3층</t>
+          <t>부산광역시 중구 해관로 3 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sso_blingnail</t>
+          <t>https://www.instagram.com/nailhagoga/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5081,13 +5033,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>650</v>
+        <v>18</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>670</v>
+        <v>19</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5096,17 +5048,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1946317931</t>
+          <t>2030742681</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946317931</t>
+          <t>https://m.place.naver.com/place/2030742681</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5118,39 +5070,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일포시즌 레푸스 남포점</t>
+          <t>니손내손</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mimongmnn@naver.com</t>
+          <t>gusalsv3v@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1498-2303</t>
+          <t>0507-1406-4146</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 50-1 5층</t>
+          <t>부산광역시 중구 대청로 85-1 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://litt.ly/refuss_nail4season_busan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5171,17 +5123,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>875</v>
+        <v>6</v>
       </c>
       <c r="Q51" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>1014</v>
+        <v>7</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5190,17 +5142,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1703326180</t>
+          <t>1044585254</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703326180</t>
+          <t>https://m.place.naver.com/place/1044585254</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5212,29 +5164,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>르메드</t>
+          <t>쿠키네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>yellowfox04@naver.com</t>
+          <t>gksrhdwn0804@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>051-417-8046</t>
+          <t>051-418-2939</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로13번길 5 1층 RE:MADE 르메드</t>
+          <t>부산광역시 영도구 대교로14번길 28</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_made.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5244,7 +5196,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5265,17 +5217,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>185</v>
+        <v>11</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5284,17 +5236,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1237521512</t>
+          <t>1954239361</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237521512</t>
+          <t>https://m.place.naver.com/place/1954239361</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5306,20 +5258,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>뷰티네일샵</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ofoiaa@naver.com</t>
-        </is>
-      </c>
+          <t>솔네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 청학북로 21 (청학동) 1층</t>
+          <t>부산광역시 영도구 태종로 422 태림맨션상가 103호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5359,13 +5307,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5374,17 +5322,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1501291375</t>
+          <t>1216411669</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501291375</t>
+          <t>https://m.place.naver.com/place/1216411669</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5396,30 +5344,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>달리뷰띠끄</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>sonmh1122@naver.com</t>
-        </is>
-      </c>
+          <t>뽀시락네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1350-2309</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 54-1 2층 203호</t>
+          <t>부산광역시 영도구 대교로14번길 21-4 1층 뽀시락네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnYigT</t>
+          <t>https://open.kakao.com/o/s1WfpFWd</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5445,17 +5393,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4157</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4552</v>
+        <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5464,17 +5412,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1025786243</t>
+          <t>1347303952</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025786243</t>
+          <t>https://m.place.naver.com/place/1347303952</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5486,29 +5434,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일에비뉴</t>
+          <t>윤아네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sk8ergirl88@naver.com</t>
+          <t>gmlwjd1902@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1324-6942</t>
+          <t>0507-1322-6563</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로48번길 3 1층 네일에비뉴</t>
+          <t>부산광역시 영도구 절영로 504 상가 206호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_auenue86/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5518,7 +5466,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5539,17 +5487,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5558,17 +5506,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1865318390</t>
+          <t>1363399967</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865318390</t>
+          <t>https://m.place.naver.com/place/1363399967</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5580,29 +5528,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>제이민뷰티</t>
+          <t>네일이떼</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>praisingcm@naver.com</t>
+          <t>mikiler486@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1414-3834</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 중구 해관로 47-1 2층</t>
+          <t>부산광역시 영도구 웃서발로 9 피아노하우스 1층 101호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://네일인스타https//instagram.com/j_min_nail?igshid=rr24r0p8o90u</t>
+          <t>http://instagram.com/nail_itte</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5637,13 +5581,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5652,17 +5596,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>269796361</t>
+          <t>1456764980</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/269796361</t>
+          <t>https://m.place.naver.com/place/1456764980</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5674,29 +5618,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>루네일공방</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>loonails@naver.com</t>
-        </is>
-      </c>
+          <t>치코네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1421-4101</t>
+          <t>0507-1379-7941</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복중앙로 3 루네일공방 1층 (창선파출소 옆골목)</t>
+          <t>부산광역시 남구 용호로216번가길 23 미광빌딩 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/loonailsfactory</t>
+          <t>https://www.instagram.com/chico_nail_?igsh=a2R0cXJ4YmUyMHRs&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5731,13 +5671,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>309</v>
+        <v>9</v>
       </c>
       <c r="Q57" t="n">
-        <v>195</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>504</v>
+        <v>13</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5746,17 +5686,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>37484954</t>
+          <t>37565672</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37484954</t>
+          <t>https://m.place.naver.com/place/37565672</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5768,29 +5708,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일살롱 문</t>
+          <t>네일반하다</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>95thvldk@naver.com</t>
+          <t>bbol_y@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1367-6993</t>
+          <t>051-915-7022</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 남구 동명로152번길 93 용호시장 1층 20호</t>
+          <t>부산광역시 영도구 남항로 18-1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_salon_moon</t>
+          <t>http://instagram.com/banhada_nail_</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5825,13 +5765,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5840,17 +5780,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1688553170</t>
+          <t>572364787</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688553170</t>
+          <t>https://m.place.naver.com/place/572364787</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5862,24 +5802,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>신디네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>zmfltmvlfhf2@naver.com</t>
-        </is>
-      </c>
+          <t>콩네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1307-0292</t>
+          <t>0507-1489-9040</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 상리로 25 동삼그린힐아파트상가 가동 105호</t>
+          <t>부산광역시 영도구 대교로40번길 8 1층 102호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5919,13 +5855,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5934,17 +5870,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1341782378</t>
+          <t>1098435819</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1341782378</t>
+          <t>https://m.place.naver.com/place/1098435819</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5956,34 +5892,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>더블랙뷰티 부민점</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>theblackbeauty@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1376-5423</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 서구 구덕로 214 3층</t>
+          <t>부산광역시 중구 흑교로75번길 4-2 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FyFcn</t>
+          <t>https://www.instagram.com/momonail0077</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6004,7 +5936,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6013,13 +5945,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R60" t="n">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6028,17 +5960,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2002868588</t>
+          <t>1050708757</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002868588</t>
+          <t>https://m.place.naver.com/place/1050708757</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6050,12 +5982,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>모모네일</t>
+          <t>손톱깎끼</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>brenda70@naver.com</t>
+          <t>dojin4538@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -6063,12 +5995,12 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 중구 흑교로75번길 4-2 1층</t>
+          <t>부산광역시 영도구 청학로 86</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momonail0077</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6078,7 +6010,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6099,17 +6031,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6118,17 +6050,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1050708757</t>
+          <t>1961112938</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050708757</t>
+          <t>https://m.place.naver.com/place/1961112938</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6140,35 +6072,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>단비네일</t>
+          <t>네일포시즌 레푸스 남포점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>danb38@naver.com</t>
+          <t>mimongmnn@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1498-2303</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 해안산책길 20</t>
+          <t>부산광역시 중구 구덕로 50-1 5층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/refuss_nail4season_busan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6189,17 +6125,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>901</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="R62" t="n">
-        <v>7</v>
+        <v>1040</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6208,17 +6144,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1536793796</t>
+          <t>1703326180</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1536793796</t>
+          <t>https://m.place.naver.com/place/1703326180</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6230,34 +6166,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일타임즈 부산 송도 해수욕장점</t>
+          <t>쁨잇</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>rina_story1@naver.com</t>
+          <t>qpt1107@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1491-4424</t>
+          <t>0507-1480-4861</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 서구 등대로 9 송도유림스카이오션더퍼스트 3층 306호</t>
+          <t>부산광역시 영도구 남항로 34 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_PxbSxhn</t>
+          <t>https://www.instagram.com/ppeumit_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6278,7 +6214,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6287,13 +6223,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R63" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6302,17 +6238,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1667862272</t>
+          <t>1931140160</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667862272</t>
+          <t>https://m.place.naver.com/place/1931140160</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6324,29 +6260,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에스더</t>
+          <t>스튜디오뭍</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>estheryoo5@naver.com</t>
+          <t>lump2000@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1396-7919</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 260 101호 상가1층(신도브래뉴아파트상가)</t>
+          <t>부산광역시 중구 대청로 97-2 3층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s.the_nail</t>
+          <t>https://www.instagram.com/m.u.u.t_</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6381,13 +6313,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6396,17 +6328,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1296125665</t>
+          <t>1912631215</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296125665</t>
+          <t>https://m.place.naver.com/place/1912631215</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6418,29 +6350,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>치코네일</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ddo_18@naver.com</t>
-        </is>
-      </c>
+          <t>손톱</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1379-7941</t>
+          <t>070-8882-4003</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용호로216번가길 23 미광빌딩 1층</t>
+          <t>부산광역시 영도구 조내기로 38-1 원우엔리치빌상가 1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chico_nail_?igsh=a2R0cXJ4YmUyMHRs&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_young4003</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6475,13 +6403,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6490,17 +6418,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>37565672</t>
+          <t>1299202573</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37565672</t>
+          <t>https://m.place.naver.com/place/1299202573</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6512,29 +6440,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>다듬다</t>
+          <t>엔피케어 부산남포점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>areumkor@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1444-1139</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 57 다듬다2층</t>
+          <t>부산광역시 중구 구덕로 40 12층 미소안 내부</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@npcare_nampo</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6544,12 +6468,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6565,17 +6489,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="R66" t="n">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6584,17 +6508,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1282118461</t>
+          <t>1102683835</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282118461</t>
+          <t>https://m.place.naver.com/place/1102683835</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6606,39 +6530,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>콩네일</t>
+          <t>모던네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>lucia_1010@naver.com</t>
+          <t>modern_nail@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0507-1489-9040</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로40번길 8 1층 102호</t>
+          <t>부산광역시 영도구 영선대로 81 1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xcjxgPG</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6654,22 +6574,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6678,17 +6598,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1098435819</t>
+          <t>1428351678</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098435819</t>
+          <t>https://m.place.naver.com/place/1428351678</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6700,25 +6620,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>스튜디오뭍</t>
+          <t>오몽네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>yein6507@naver.com</t>
+          <t>olmang_nail@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1351-4790</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 97-2 3층</t>
+          <t>부산광역시 영도구 동삼로 31 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/m.u.u.t_</t>
+          <t>https://blog.naver.com/olmang_nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6733,7 +6657,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6753,13 +6677,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>312</v>
+        <v>522</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="R68" t="n">
-        <v>317</v>
+        <v>546</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6768,17 +6692,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1912631215</t>
+          <t>1539347427</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912631215</t>
+          <t>https://m.place.naver.com/place/1539347427</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6790,30 +6714,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일하고가</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>fromantic@naver.com</t>
-        </is>
-      </c>
+          <t>더블랙뷰티 부민점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1376-5423</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 중구 해관로 3 1층</t>
+          <t>부산광역시 서구 구덕로 214 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhagoga/</t>
+          <t>http://pf.kakao.com/_FyFcn</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6834,7 +6758,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6843,13 +6767,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6858,17 +6782,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2030742681</t>
+          <t>2002868588</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030742681</t>
+          <t>https://m.place.naver.com/place/2002868588</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6880,34 +6804,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>넌네일</t>
+          <t>미쯔네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>qweertyu1@naver.com</t>
+          <t>mizz_nail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1317-2372</t>
+          <t>0507-1388-3448</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 365 (청학동) 1층 넌네일</t>
+          <t>부산광역시 중구 광복로 47-1 3층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/nunnail</t>
+          <t>https://blog.naver.com/mizz_nail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6937,13 +6861,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6952,17 +6876,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2049417397</t>
+          <t>1942024821</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049417397</t>
+          <t>https://m.place.naver.com/place/1942024821</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6974,29 +6898,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>손꽃풀네일</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>bongjuyha@naver.com</t>
-        </is>
-      </c>
+          <t>오늘,네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1348-6215</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 72 1층</t>
+          <t>부산광역시 영도구 대교로 15 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bongjuyha</t>
+          <t>http://www.instagram.com/2day__nail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7011,7 +6927,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7031,13 +6947,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7046,17 +6962,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1289134648</t>
+          <t>1924350921</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1289134648</t>
+          <t>https://m.place.naver.com/place/1924350921</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7068,29 +6984,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>뽀시락네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>yujin1430@naver.com</t>
-        </is>
-      </c>
+          <t>손톱이야기</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1350-2309</t>
+          <t>051-417-7005</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로14번길 21-4 1층 뽀시락네일</t>
+          <t>부산광역시 영도구 절영로101번길 38</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1WfpFWd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7100,7 +7012,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7116,7 +7028,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7125,13 +7037,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7140,17 +7052,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1347303952</t>
+          <t>36925644</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347303952</t>
+          <t>https://m.place.naver.com/place/36925644</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7162,25 +7074,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>손톱</t>
+          <t>네일살롱 문</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>070-8882-4003</t>
+          <t>0507-1367-6993</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 조내기로 38-1 원우엔리치빌상가 1층</t>
+          <t>부산광역시 남구 동명로152번길 93 용호시장 1층 20호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_young4003</t>
+          <t>https://www.instagram.com/nail_salon_moon</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7215,13 +7127,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R73" t="n">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7230,17 +7142,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1299202573</t>
+          <t>1688553170</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299202573</t>
+          <t>https://m.place.naver.com/place/1688553170</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7252,34 +7164,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The GRIDA</t>
+          <t>네일타임즈 부산 송도 해수욕장점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>the-grida@naver.com</t>
+          <t>rina_story1@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1393-7300</t>
+          <t>0507-1491-4424</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중구로 22 창선상가1층</t>
+          <t>부산광역시 서구 등대로 9 송도유림스카이오션더퍼스트 3층 306호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/the-grida</t>
+          <t>https://pf.kakao.com/_PxbSxhn</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7289,7 +7201,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7300,22 +7212,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7324,17 +7236,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1992166482</t>
+          <t>1667862272</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992166482</t>
+          <t>https://m.place.naver.com/place/1667862272</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7346,29 +7258,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>윤아네일</t>
+          <t>네일온나</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gmlwjd1902@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1322-6563</t>
+          <t>0507-1383-4154</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 504 상가 206호</t>
+          <t>부산광역시 중구 구덕로 51 3층 네일온나</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_on_na/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7378,7 +7290,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7399,17 +7311,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7418,17 +7330,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1363399967</t>
+          <t>1810946003</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363399967</t>
+          <t>https://m.place.naver.com/place/1810946003</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7440,29 +7352,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>눈네일</t>
+          <t>나나뷰티살롱</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>yunimil@naver.com</t>
+          <t>rosyn_@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1350-2086</t>
+          <t>0507-1336-2115</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 중구 해관로 22-1 3층</t>
+          <t>부산광역시 영도구 절영로 557 삼창파크맨션 상가101호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noonnail</t>
+          <t>https://www.instagram.com/nana2115__</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7497,13 +7409,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="R76" t="n">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7512,17 +7424,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1509715865</t>
+          <t>1829607863</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509715865</t>
+          <t>https://m.place.naver.com/place/1829607863</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
